--- a/projectB-study1-demo-survey-2015a.xlsx
+++ b/projectB-study1-demo-survey-2015a.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thomas\Dropbox\2020-431\431-projB-study1-example\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thomas\Dropbox\2020-431\431-projectB-demo-study1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BA41859-BD1A-465A-B26D-65B9C333524B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D1E401-4334-4DF8-A130-3064C13197D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey2015raw1" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
     <t>english</t>
   </si>
   <si>
-    <t>prior.r</t>
-  </si>
-  <si>
     <t>height</t>
   </si>
   <si>
@@ -179,12 +176,15 @@
   </si>
   <si>
     <t>Running</t>
+  </si>
+  <si>
+    <t>r.before</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1036,55 +1036,55 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -1092,16 +1092,16 @@
         <v>501</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>1987</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
       </c>
       <c r="F2">
         <v>68.099999999999994</v>
@@ -1116,19 +1116,19 @@
         <v>95</v>
       </c>
       <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -1157,16 +1157,16 @@
         <v>502</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>1992</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>67</v>
@@ -1181,19 +1181,19 @@
         <v>10</v>
       </c>
       <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
         <v>29</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1222,16 +1222,16 @@
         <v>503</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>1985</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>62.5</v>
@@ -1246,19 +1246,19 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
         <v>34</v>
       </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         <v>504</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1986</v>
       </c>
       <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
       </c>
       <c r="F5">
         <v>22.83</v>
@@ -1311,19 +1311,19 @@
         <v>100</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" t="s">
         <v>34</v>
       </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O5">
         <v>20</v>
@@ -1352,16 +1352,16 @@
         <v>505</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>1992</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>70</v>
@@ -1376,19 +1376,19 @@
         <v>20</v>
       </c>
       <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
         <v>37</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>38</v>
       </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O6">
         <v>80</v>
@@ -1417,16 +1417,16 @@
         <v>506</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>1991</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>73</v>
@@ -1441,19 +1441,19 @@
         <v>10</v>
       </c>
       <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
         <v>40</v>
       </c>
-      <c r="K7" t="s">
-        <v>41</v>
-      </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>507</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>1983</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8">
         <v>74</v>
@@ -1506,19 +1506,19 @@
         <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
         <v>26</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>27</v>
-      </c>
-      <c r="N8" t="s">
-        <v>28</v>
       </c>
       <c r="O8">
         <v>50</v>
@@ -1547,16 +1547,16 @@
         <v>508</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>1990</v>
       </c>
       <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9">
         <v>70</v>
@@ -1571,19 +1571,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9">
         <v>60</v>
@@ -1612,16 +1612,16 @@
         <v>509</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1993</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10">
         <v>64</v>
@@ -1636,19 +1636,19 @@
         <v>60</v>
       </c>
       <c r="J10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
         <v>43</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" t="s">
-        <v>44</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1677,16 +1677,16 @@
         <v>510</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1988</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11">
         <v>69</v>
@@ -1701,19 +1701,19 @@
         <v>50</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
         <v>26</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>27</v>
-      </c>
-      <c r="N11" t="s">
-        <v>28</v>
       </c>
       <c r="O11">
         <v>30</v>
@@ -1742,16 +1742,16 @@
         <v>511</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>1991</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <v>65</v>
@@ -1766,19 +1766,19 @@
         <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1807,16 +1807,16 @@
         <v>512</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>1992</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13">
         <v>65</v>
@@ -1831,19 +1831,19 @@
         <v>20</v>
       </c>
       <c r="J13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" t="s">
         <v>27</v>
-      </c>
-      <c r="N13" t="s">
-        <v>28</v>
       </c>
       <c r="O13">
         <v>50</v>
@@ -1872,16 +1872,16 @@
         <v>513</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>1988</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14">
         <v>61.417299999999997</v>
@@ -1896,19 +1896,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L14" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" t="s">
         <v>34</v>
       </c>
-      <c r="M14" t="s">
-        <v>35</v>
-      </c>
       <c r="N14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1937,16 +1937,16 @@
         <v>514</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>1993</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15">
         <v>64</v>
@@ -1961,19 +1961,19 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
         <v>26</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>27</v>
-      </c>
-      <c r="N15" t="s">
-        <v>28</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2002,16 +2002,16 @@
         <v>515</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>1986</v>
       </c>
       <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
         <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
       </c>
       <c r="F16">
         <v>68</v>
@@ -2026,19 +2026,19 @@
         <v>70</v>
       </c>
       <c r="J16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" t="s">
         <v>25</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>26</v>
       </c>
-      <c r="M16" t="s">
-        <v>27</v>
-      </c>
       <c r="N16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O16">
         <v>60</v>
@@ -2067,16 +2067,16 @@
         <v>516</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>1993</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17">
         <v>71</v>
@@ -2091,19 +2091,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M17" t="s">
         <v>48</v>
       </c>
-      <c r="K17" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" t="s">
-        <v>39</v>
-      </c>
-      <c r="M17" t="s">
-        <v>49</v>
-      </c>
       <c r="N17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>517</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>1993</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18">
         <v>72</v>
@@ -2156,19 +2156,19 @@
         <v>20</v>
       </c>
       <c r="J18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K18" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" t="s">
         <v>30</v>
       </c>
-      <c r="L18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M18" t="s">
-        <v>31</v>
-      </c>
       <c r="N18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O18">
         <v>90</v>
@@ -2197,16 +2197,16 @@
         <v>518</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>1983</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F19">
         <v>72</v>
@@ -2221,19 +2221,19 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O19">
         <v>20</v>
@@ -2262,16 +2262,16 @@
         <v>519</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>1976</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20">
         <v>62</v>
@@ -2286,19 +2286,19 @@
         <v>10</v>
       </c>
       <c r="J20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" t="s">
         <v>25</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>26</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>27</v>
-      </c>
-      <c r="N20" t="s">
-        <v>28</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -2327,16 +2327,16 @@
         <v>520</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21">
         <v>1988</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21">
         <v>66</v>
@@ -2351,19 +2351,19 @@
         <v>40</v>
       </c>
       <c r="J21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" t="s">
         <v>43</v>
-      </c>
-      <c r="K21" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" t="s">
-        <v>44</v>
       </c>
       <c r="O21">
         <v>0</v>
